--- a/data/test_papers/test_papers_data_sources.xlsx
+++ b/data/test_papers/test_papers_data_sources.xlsx
@@ -27,12 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
   <si>
     <t>#</t>
   </si>
   <si>
-    <t>COMPARE TYPE</t>
+    <t>note</t>
   </si>
   <si>
     <t>Paper</t>
@@ -44,30 +44,6 @@
     <t>factor name</t>
   </si>
   <si>
-    <t>Databases / Sources</t>
-  </si>
-  <si>
-    <t>C Z PERFORMANCE</t>
-  </si>
-  <si>
-    <t>HXZ PERFORMANCE</t>
-  </si>
-  <si>
-    <t>Sample Period</t>
-  </si>
-  <si>
-    <t>Sample Size / Universe Filters</t>
-  </si>
-  <si>
-    <t>Key Variables (with codes)</t>
-  </si>
-  <si>
-    <t>Data Processing Details</t>
-  </si>
-  <si>
-    <t>Special Notes</t>
-  </si>
-  <si>
     <t>两篇论文难得达成一致的案例</t>
   </si>
   <si>
@@ -80,67 +56,6 @@
     <t>GP</t>
   </si>
   <si>
-    <t>compustat,  crsp</t>
-  </si>
-  <si>
-    <t>0.30  2.38</t>
-  </si>
-  <si>
-    <t>0.20   1.85</t>
-  </si>
-  <si>
-    <t>HXZ 标准化结果:直接点名"fails to replicate"； C&amp;Z 原始方法复现:t = 3.29(原始论文 t = 5.59),归为 Clear Predictor,成功复现</t>
-  </si>
-  <si>
-    <t>Value investing: The use of historical financial statement
-information to separate winners from losers</t>
-  </si>
-  <si>
-    <t>Piotroski (2000)</t>
-  </si>
-  <si>
-    <t>PS</t>
-  </si>
-  <si>
-    <t>0.92  3.29</t>
-  </si>
-  <si>
-    <t>0.29   1.11</t>
-  </si>
-  <si>
-    <t>"数据版本分歧"(Data Vintage Divergence)——因子在两次复现之间结果不一致,但差异既不能用权重/breakpoint 解释,也不能完全用滞后结构解释,而是源于底层数据源(尤其 IBES 这类会被回溯修订的数据库)在不同抓取时间点内容不同。这类分歧你的 agent 理论上无法通过纯方法论比对来发现,</t>
-  </si>
-  <si>
-    <t>Expectations and the cross-section of stock return</t>
-  </si>
-  <si>
-    <t>La Porta (1996)</t>
-  </si>
-  <si>
-    <t>fgr5yrLag</t>
-  </si>
-  <si>
-    <t>compustat,  crsp, IBES</t>
-  </si>
-  <si>
-    <t>0.83  2.06</t>
-  </si>
-  <si>
-    <t>-0.66     -1.6</t>
-  </si>
-  <si>
-    <t>HXZ 判定失败,C&amp;Z 用原始方法论判定成功</t>
-  </si>
-  <si>
-    <t>Debt/equity ratio and expected common stock returns: Empirical evidence</t>
-  </si>
-  <si>
-    <t>Bhandari (1988)</t>
-  </si>
-  <si>
-    <t>Leverage</t>
-  </si>
-  <si>
     <t>HXZ (I/A):NYSE-VW t=2.89(显著),但量级只有原文 VW 版本的 42%(-0.44% vs -1.05%)； C&amp;Z:季度版本 AssetGrowth_q,t=4.84,强</t>
   </si>
   <si>
@@ -153,9 +68,6 @@
     <t>AssetGrowth</t>
   </si>
   <si>
-    <t>1.5    7.64</t>
-  </si>
-  <si>
     <t>严重分歧:HXZ 判定失败,C&amp;Z 用原始方法论判定成功</t>
   </si>
   <si>
@@ -165,19 +77,37 @@
     <t>Dichev (1998)</t>
   </si>
   <si>
-    <t>OScore</t>
-  </si>
-  <si>
-    <t>都失败</t>
-  </si>
-  <si>
-    <t>In search of distress risk</t>
-  </si>
-  <si>
-    <t>Campbell, Hilscher, Szilagyi (2008)</t>
-  </si>
-  <si>
-    <t>FailureProbability</t>
+    <t>ZScore/oscore</t>
+  </si>
+  <si>
+    <t>都成功</t>
+  </si>
+  <si>
+    <t>Returns to buying winners and selling losers- Implications for stock market efficiency</t>
+  </si>
+  <si>
+    <t>Jegadeesh and Titman (1993, JF)</t>
+  </si>
+  <si>
+    <t>momentum</t>
+  </si>
+  <si>
+    <t>Liquidity and stock returns: An alternative test</t>
+  </si>
+  <si>
+    <t>Datar, V. T., Naik, N. Y., and Radcliffe, R. (1998)</t>
+  </si>
+  <si>
+    <t>ShareVol</t>
+  </si>
+  <si>
+    <t>Contrarian Investment, Extrapolation, and Risk</t>
+  </si>
+  <si>
+    <t>Lakonishok, Josef, Andrei Shleifer, and Robert W. Vishny (1994)</t>
+  </si>
+  <si>
+    <t>MeanRankRevGrowth</t>
   </si>
 </sst>
 </file>
@@ -190,7 +120,7 @@
     <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -220,13 +150,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -371,17 +294,29 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4472C4"/>
         <bgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -716,70 +651,64 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -788,10 +717,10 @@
     <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -800,10 +729,10 @@
     <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -812,10 +741,10 @@
     <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -824,10 +753,10 @@
     <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -836,39 +765,43 @@
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1215,364 +1148,239 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="8.875" customWidth="1"/>
-    <col min="2" max="2" width="48.7109375" customWidth="1"/>
+    <col min="2" max="2" width="45.703125" customWidth="1"/>
     <col min="3" max="3" width="69.921875" customWidth="1"/>
     <col min="4" max="4" width="35.3515625" customWidth="1"/>
     <col min="5" max="5" width="20.0859375" customWidth="1"/>
-    <col min="6" max="8" width="34" customWidth="1"/>
-    <col min="9" max="9" width="28" customWidth="1"/>
-    <col min="10" max="11" width="40" customWidth="1"/>
-    <col min="12" max="12" width="55" customWidth="1"/>
-    <col min="13" max="13" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" spans="1:13">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="20" customHeight="1" spans="1:5">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" ht="17" spans="1:5">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="C2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="E2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" ht="17" spans="1:13">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-    </row>
-    <row r="3" ht="51" spans="1:13">
+    </row>
+    <row r="3" s="1" customFormat="1" ht="51" spans="1:5">
       <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="17.2" spans="1:5">
+      <c r="A4" s="6">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" ht="17" spans="1:5">
+      <c r="A5" s="6">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="3" t="s">
+    </row>
+    <row r="6" customFormat="1" ht="34" spans="1:5">
+      <c r="A6" s="6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="3" t="s">
+    </row>
+    <row r="7" customFormat="1" ht="34" spans="1:5">
+      <c r="A7" s="6">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="D7" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-    </row>
-    <row r="4" ht="100" customHeight="1" spans="1:13">
-      <c r="A4" s="3">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="E7" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-    </row>
-    <row r="5" ht="17" spans="1:13">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-    </row>
-    <row r="6" ht="51" spans="1:13">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-    </row>
-    <row r="7" ht="17.2" spans="1:13">
-      <c r="A7" s="3">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-    </row>
-    <row r="8" ht="17.2" spans="1:13">
-      <c r="A8" s="3">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="3">
-        <v>5</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="3">
-        <v>6</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="3">
-        <v>7</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="3">
-        <v>8</v>
-      </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="3">
-        <v>9</v>
-      </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="3">
-        <v>10</v>
-      </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
+    </row>
+    <row r="8" customFormat="1" spans="1:5">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+    </row>
+    <row r="9" customFormat="1" spans="1:5">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+    </row>
+    <row r="10" customFormat="1" spans="1:5">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+    </row>
+    <row r="12" ht="100" customHeight="1" spans="1:5">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="8"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="8"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+    </row>
+    <row r="15" ht="17.2" spans="1:5">
+      <c r="A15" s="6"/>
+      <c r="B15"/>
+      <c r="C15" s="6"/>
+      <c r="D15"/>
+      <c r="E15" s="7"/>
+    </row>
+    <row r="16" ht="17.2" spans="1:5">
+      <c r="A16" s="6"/>
+      <c r="B16"/>
+      <c r="C16" s="6"/>
+      <c r="D16"/>
+      <c r="E16" s="7"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/test_papers/test_papers_data_sources.xlsx
+++ b/data/test_papers/test_papers_data_sources.xlsx
@@ -1,302 +1,203 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="23760"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="23760" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Detailed Data Sources_new" sheetId="4" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed Data Sources_new" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>note</t>
-  </si>
-  <si>
-    <t>Paper</t>
-  </si>
-  <si>
-    <t>Citation</t>
-  </si>
-  <si>
-    <t>factor name</t>
-  </si>
-  <si>
-    <t>两篇论文难得达成一致的案例</t>
-  </si>
-  <si>
-    <t>The other side of value: The gross profitability premium</t>
-  </si>
-  <si>
-    <t>Novy-Marx (2013)</t>
-  </si>
-  <si>
-    <t>GP</t>
-  </si>
-  <si>
-    <t>HXZ (I/A):NYSE-VW t=2.89(显著),但量级只有原文 VW 版本的 42%(-0.44% vs -1.05%)； C&amp;Z:季度版本 AssetGrowth_q,t=4.84,强</t>
-  </si>
-  <si>
-    <t>Asset Growth and Stock Returns</t>
-  </si>
-  <si>
-    <t>Cooper, Gulen and Schill (2008)</t>
-  </si>
-  <si>
-    <t>AssetGrowth</t>
-  </si>
-  <si>
-    <t>严重分歧:HXZ 判定失败,C&amp;Z 用原始方法论判定成功</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Is the risk of bankruptcy a systematic risk </t>
-  </si>
-  <si>
-    <t>Dichev (1998)</t>
-  </si>
-  <si>
-    <t>ZScore/oscore</t>
-  </si>
-  <si>
-    <t>都成功</t>
-  </si>
-  <si>
-    <t>Returns to buying winners and selling losers- Implications for stock market efficiency</t>
-  </si>
-  <si>
-    <t>Jegadeesh and Titman (1993, JF)</t>
-  </si>
-  <si>
-    <t>momentum</t>
-  </si>
-  <si>
-    <t>Liquidity and stock returns: An alternative test</t>
-  </si>
-  <si>
-    <t>Datar, V. T., Naik, N. Y., and Radcliffe, R. (1998)</t>
-  </si>
-  <si>
-    <t>ShareVol</t>
-  </si>
-  <si>
-    <t>Contrarian Investment, Extrapolation, and Risk</t>
-  </si>
-  <si>
-    <t>Lakonishok, Josef, Andrei Shleifer, and Robert W. Vishny (1994)</t>
-  </si>
-  <si>
-    <t>MeanRankRevGrowth</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="23">
     <font>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Utopia"/>
       <charset val="134"/>
-    </font>
-    <font>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <color rgb="FF333333"/>
       <sz val="11.4"/>
-      <color rgb="FF333333"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="37">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -636,172 +537,172 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -855,11 +756,74 @@
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1146,244 +1110,300 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="8.875" customWidth="1"/>
-    <col min="2" max="2" width="45.703125" customWidth="1"/>
-    <col min="3" max="3" width="69.921875" customWidth="1"/>
-    <col min="4" max="4" width="35.3515625" customWidth="1"/>
-    <col min="5" max="5" width="20.0859375" customWidth="1"/>
+    <col width="8.875" customWidth="1" min="1" max="1"/>
+    <col width="45.703125" customWidth="1" min="2" max="2"/>
+    <col width="69.921875" customWidth="1" min="3" max="3"/>
+    <col width="35.3515625" customWidth="1" min="4" max="4"/>
+    <col width="20.0859375" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" spans="1:5">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Citation</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>factor name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17" customFormat="1" customHeight="1" s="1">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>两篇论文罕见一致的案例：HXZ的Gpa在全部四种断点/权重组合下均显著（NYSE-VW t=2.63, NYSE-EW t=4.35, All-VW t=2.83, All-EW t=3.29），未出现VW失效、EW显著的典型microcap模式；C&amp;Z归类为clear predictor，t=2.38（样本1963-2010），与原文自身VW长短组合t=2.5高度吻合。断点、权重、样本期选择对该因子结果影响都很小，是本组中少见的、两种方法论都不敏感的稳健因子。</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>The other side of value: The gross profitability premium</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Novy-Marx (2013)</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>GP</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="51" customFormat="1" customHeight="1" s="1">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>HXZ用I/A变量：NYSE-VW t=2.89(显著)，但量级仅为原文VW版本的42%(-0.44% vs -1.05%)，其余断点/权重组合下量级同样明显衰减；C&amp;Z有两个需区分的条目——(1)年度原始构造AssetGrowth（Table2, clear predictor）：样本1968-2003，t=7.64，与原文自身port sort的t=8.5高度吻合；(2)季度重构版AssetGrowth_q（Table4, Indirect Evidence/HXZ variant，即C&amp;Z在测试HXZ自创的季度化变量，而非Cooper-Gulen-Schill原始年度变量）：t=4.84。因此表面的HXZ-vs-C&amp;Z分歧，实际混合了断点/权重效应(年度对比下HXZ量级仅42%)与变量重构效应(年度vs季度)两个不同维度，值得在论文中分开讨论。</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Asset Growth and Stock Returns</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Cooper, Gulen and Schill (2008)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>AssetGrowth</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17.2" customHeight="1">
+      <c r="A4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>需区分两个变量，现有note把二者混为一谈：(1) O-score(Dichev原始构造，真正的分歧案例)：HXZ在全部四种断点/权重组合下均不显著(NYSE-VW t=0.48, NYSE-EW t=0.04, All-VW t=1.82, All-EW t=0.40)，说明失败并非断点或权重选择所致；C&amp;Z的OScore为clear predictor,t=3.39(样本1981-1995)。可能原因是Dichev原文采用非对称的“最高10%-最低70%”分组，而HXZ改用标准对称十分位。(2) Z-score：C&amp;Z自身也将其归类为Not Predictor(t≈1.20-1.59)，与HXZ失败结论一致，并非分歧案例——建议本行聚焦O-score，或将两者拆成独立两行。</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Is the risk of bankruptcy a systematic risk </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Dichev (1998)</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>ZScore/oscore</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17" customHeight="1">
+      <c r="A5" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="17" spans="1:5">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>都成功且量级也接近：HXZ的R66(前6个月收益排序、持有6个月)组合，NYSE-VW 0.82%/月,t=3.5(扩展样本1967-2016)；在原文对应的较短样本+All-EW下达到1.18%/月,t=4.22，与原文Jegadeesh-Titman(1993)自身报告的1.1%/月,t=3.61非常接近；HXZ原始(较短)样本NYSE-VW为1.06%/月,t=3.82。C&amp;Z采用与原文一致的单一排序(single sort)构造，而非Fama-French式2x3双重排序，且发现该动量组合与其他long-short组合的相关性上限约0.6(仅少数组合达到)，支持其作为独立因子的稳健性。断点、权重、排序方式在此因子上带来的分歧都很小。</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Returns to buying winners and selling losers- Implications for stock market efficiency</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Jegadeesh and Titman (1993, JF)</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>原文DNR(1998)本身并非标准VW/EW quantile long-short检验：换手率=3个月滚动平均成交量/流通股数(t-3至t-1月)，核心检验是个股层面月度Fama-MacBeth横截面回归(控制规模、B/M)，全文从未报告VW或EW组合收益；文中基于Amihud-Mendelson(1986)方法的beta分组仅用于估计beta，与换手率排序无关。样本为NYSE非金融股1962.7-1991.12，月频。HXZ将其重构为Tur1并做标准quantile long-short：NYSE-VW t=0.61(失败)，All-EW t=4.22(强，呈现典型microcap驱动模式)；C&amp;Z的ShareVol为clear predictor,t=3.87(样本1962-1991)，原文自身univariate回归t=8.9。由于原文根本不存在VW/EW组合排序这一维度，HXZ与C&amp;Z各自的quantile框架都是后续再造而非对原文的还原，这一点本身就是论文里值得强调的方法论发现。</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Liquidity and stock returns: An alternative test</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Datar, V. T., Naik, N. Y., and Radcliffe, R. (1998)</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>ShareVol</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="51" spans="1:5">
-      <c r="A3" s="3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" customFormat="1" ht="17.2" spans="1:5">
-      <c r="A4" s="6">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" customFormat="1" ht="17" spans="1:5">
-      <c r="A5" s="6">
-        <v>3</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" customFormat="1" ht="34" spans="1:5">
-      <c r="A6" s="6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" customFormat="1" ht="34" spans="1:5">
-      <c r="A7" s="6">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" customFormat="1" spans="1:5">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-    </row>
-    <row r="9" customFormat="1" spans="1:5">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-    </row>
-    <row r="10" customFormat="1" spans="1:5">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-    </row>
-    <row r="12" ht="100" customHeight="1" spans="1:5">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="8"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="8"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-    </row>
-    <row r="15" ht="17.2" spans="1:5">
-      <c r="A15" s="6"/>
-      <c r="B15"/>
-      <c r="C15" s="6"/>
-      <c r="D15"/>
-      <c r="E15" s="7"/>
-    </row>
-    <row r="16" ht="17.2" spans="1:5">
-      <c r="A16" s="6"/>
-      <c r="B16"/>
-      <c r="C16" s="6"/>
-      <c r="D16"/>
-      <c r="E16" s="7"/>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>原文与C&amp;Z均采用双重排序(double sort)构造，区别于同表其他单一排序因子。HXZ的Sr变量(5年销售增长率排名)：NYSE-VW t=1.08(失败)，NYSE-EW t=3.52，All-EW t=3.65，呈现典型的microcap驱动模式(EW远强于VW，全市场断点强于NYSE断点)；C&amp;Z的MeanRankRevGrowth为clear predictor(双重排序)，t=3.94(样本1968-1990)，与原文自身双重排序t=4.5高度吻合。分歧主要来自断点(NYSE vs 全市场)与权重(VW vs EW)选择的叠加效应。</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Contrarian Investment, Extrapolation, and Risk</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Lakonishok, Josef, Andrei Shleifer, and Robert W. Vishny (1994)</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>MeanRankRevGrowth</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+    </row>
+    <row r="12" ht="100" customHeight="1">
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="17.2" customHeight="1">
+      <c r="A15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="E15" s="7" t="n"/>
+    </row>
+    <row r="16" ht="17.2" customHeight="1">
+      <c r="A16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="E16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n"/>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/data/test_papers/test_papers_data_sources.xlsx
+++ b/data/test_papers/test_papers_data_sources.xlsx
@@ -1,203 +1,308 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="23760" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowHeight="23760"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed Data Sources_new" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Detailed Data Sources_new" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>Paper</t>
+  </si>
+  <si>
+    <t>Citation</t>
+  </si>
+  <si>
+    <t>factor name</t>
+  </si>
+  <si>
+    <t>原文DNR(1998)本身并非标准VW/EW quantile long-short检验：换手率=3个月滚动平均成交量/流通股数(t-3至t-1月)，核心检验是个股层面月度Fama-MacBeth横截面回归(控制规模、B/M)，全文从未报告VW或EW组合收益；文中基于Amihud-Mendelson(1986)方法的beta分组仅用于估计beta，与换手率排序无关。样本为NYSE非金融股1962.7-1991.12，月频。HXZ将其重构为Tur1并做标准quantile long-short：NYSE-VW t=0.61(失败)，All-EW t=4.22(强，呈现典型microcap驱动模式)；C&amp;Z的ShareVol为clear predictor,t=3.87(样本1962-1991)，原文自身univariate回归t=8.9。由于原文根本不存在VW/EW组合排序这一维度，HXZ与C&amp;Z各自的quantile框架都是后续再造而非对原文的还原，这一点本身就是论文里值得强调的方法论发现。</t>
+  </si>
+  <si>
+    <t>Liquidity and stock returns: An alternative test</t>
+  </si>
+  <si>
+    <t>Datar, V. T., Naik, N. Y., and Radcliffe, R. (1998)</t>
+  </si>
+  <si>
+    <t>ShareVol</t>
+  </si>
+  <si>
+    <t>HXZ用I/A变量：NYSE-VW t=2.89(显著)，但量级仅为原文VW版本的42%(-0.44% vs -1.05%)，其余断点/权重组合下量级同样明显衰减；C&amp;Z有两个需区分的条目——(1)年度原始构造AssetGrowth（Table2, clear predictor）：样本1968-2003，t=7.64，与原文自身port sort的t=8.5高度吻合；(2)季度重构版AssetGrowth_q（Table4, Indirect Evidence/HXZ variant，即C&amp;Z在测试HXZ自创的季度化变量，而非Cooper-Gulen-Schill原始年度变量）：t=4.84。因此表面的HXZ-vs-C&amp;Z分歧，实际混合了断点/权重效应(年度对比下HXZ量级仅42%)与变量重构效应(年度vs季度)两个不同维度，值得在论文中分开讨论。</t>
+  </si>
+  <si>
+    <t>Asset Growth and Stock Returns</t>
+  </si>
+  <si>
+    <t>Cooper, Gulen and Schill (2008)</t>
+  </si>
+  <si>
+    <t>AssetGrowth</t>
+  </si>
+  <si>
+    <t>原文与C&amp;Z均采用双重排序(double sort)构造，区别于同表其他单一排序因子。HXZ的Sr变量(5年销售增长率排名)：NYSE-VW t=1.08(失败)，NYSE-EW t=3.52，All-EW t=3.65，呈现典型的microcap驱动模式(EW远强于VW，全市场断点强于NYSE断点)；C&amp;Z的MeanRankRevGrowth为clear predictor(双重排序)，t=3.94(样本1968-1990)，与原文自身双重排序t=4.5高度吻合。分歧主要来自断点(NYSE vs 全市场)与权重(VW vs EW)选择的叠加效应。</t>
+  </si>
+  <si>
+    <t>Contrarian Investment, Extrapolation, and Risk</t>
+  </si>
+  <si>
+    <t>Lakonishok, Josef, Andrei Shleifer, and Robert W. Vishny (1994)</t>
+  </si>
+  <si>
+    <t>MeanRankRevGrowth</t>
+  </si>
+  <si>
+    <t>两篇论文罕见一致的案例：HXZ的Gpa在全部四种断点/权重组合下均显著（NYSE-VW t=2.63, NYSE-EW t=4.35, All-VW t=2.83, All-EW t=3.29），未出现VW失效、EW显著的典型microcap模式；C&amp;Z归类为clear predictor，t=2.38（样本1963-2010），与原文自身VW长短组合t=2.5高度吻合。断点、权重、样本期选择对该因子结果影响都很小，是本组中少见的、两种方法论都不敏感的稳健因子。</t>
+  </si>
+  <si>
+    <t>The other side of value: The gross profitability premium</t>
+  </si>
+  <si>
+    <t>Novy-Marx (2013)</t>
+  </si>
+  <si>
+    <t>GP</t>
+  </si>
+  <si>
+    <t>需区分两个变量，现有note把二者混为一谈：(1) O-score(Dichev原始构造，真正的分歧案例)：HXZ在全部四种断点/权重组合下均不显著(NYSE-VW t=0.48, NYSE-EW t=0.04, All-VW t=1.82, All-EW t=0.40)，说明失败并非断点或权重选择所致；C&amp;Z的OScore为clear predictor,t=3.39(样本1981-1995)。可能原因是Dichev原文采用非对称的“最高10%-最低70%”分组，而HXZ改用标准对称十分位。(2) Z-score：C&amp;Z自身也将其归类为Not Predictor(t≈1.20-1.59)，与HXZ失败结论一致，并非分歧案例——建议本行聚焦O-score，或将两者拆成独立两行。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the risk of bankruptcy a systematic risk </t>
+  </si>
+  <si>
+    <t>Dichev (1998)</t>
+  </si>
+  <si>
+    <t>ZScore/oscore</t>
+  </si>
+  <si>
+    <t>都成功且量级也接近：HXZ的R66(前6个月收益排序、持有6个月)组合，NYSE-VW 0.82%/月,t=3.5(扩展样本1967-2016)；在原文对应的较短样本+All-EW下达到1.18%/月,t=4.22，与原文Jegadeesh-Titman(1993)自身报告的1.1%/月,t=3.61非常接近；HXZ原始(较短)样本NYSE-VW为1.06%/月,t=3.82。C&amp;Z采用与原文一致的单一排序(single sort)构造，而非Fama-French式2x3双重排序，且发现该动量组合与其他long-short组合的相关性上限约0.6(仅少数组合达到)，支持其作为独立因子的稳健性。断点、权重、排序方式在此因子上带来的分歧都很小。</t>
+  </si>
+  <si>
+    <t>Returns to buying winners and selling losers- Implications for stock market efficiency</t>
+  </si>
+  <si>
+    <t>Jegadeesh and Titman (1993, JF)</t>
+  </si>
+  <si>
+    <t>momentum</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="23">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Utopia"/>
       <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-    </font>
-    <font>
+    </font>
+    <font>
+      <sz val="11.4"/>
+      <color rgb="FF333333"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <color rgb="FF333333"/>
-      <sz val="11.4"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <b val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="Calibri"/>
       <charset val="134"/>
-      <b val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="Calibri"/>
       <charset val="134"/>
-      <b val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="Calibri"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <b val="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <b val="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <b val="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <b val="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
-    <fill>
-      <patternFill/>
+  <fills count="36">
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -212,12 +317,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF4472C4"/>
         <bgColor rgb="FF4472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -537,172 +636,169 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -756,74 +852,11 @@
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1110,300 +1143,226 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E22"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
-    <col width="8.875" customWidth="1" min="1" max="1"/>
-    <col width="45.703125" customWidth="1" min="2" max="2"/>
-    <col width="69.921875" customWidth="1" min="3" max="3"/>
-    <col width="35.3515625" customWidth="1" min="4" max="4"/>
-    <col width="20.0859375" customWidth="1" min="5" max="5"/>
+    <col min="1" max="1" width="8.875" customWidth="1"/>
+    <col min="2" max="2" width="65.6953125" customWidth="1"/>
+    <col min="3" max="3" width="69.921875" customWidth="1"/>
+    <col min="4" max="4" width="35.3515625" customWidth="1"/>
+    <col min="5" max="5" width="20.0859375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Citation</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>factor name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="17" customFormat="1" customHeight="1" s="1">
-      <c r="A2" s="3" t="n">
+    <row r="1" ht="20" customHeight="1" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>两篇论文罕见一致的案例：HXZ的Gpa在全部四种断点/权重组合下均显著（NYSE-VW t=2.63, NYSE-EW t=4.35, All-VW t=2.83, All-EW t=3.29），未出现VW失效、EW显著的典型microcap模式；C&amp;Z归类为clear predictor，t=2.38（样本1963-2010），与原文自身VW长短组合t=2.5高度吻合。断点、权重、样本期选择对该因子结果影响都很小，是本组中少见的、两种方法论都不敏感的稳健因子。</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>The other side of value: The gross profitability premium</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>Novy-Marx (2013)</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>GP</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="51" customFormat="1" customHeight="1" s="1">
-      <c r="A3" s="3" t="n">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>HXZ用I/A变量：NYSE-VW t=2.89(显著)，但量级仅为原文VW版本的42%(-0.44% vs -1.05%)，其余断点/权重组合下量级同样明显衰减；C&amp;Z有两个需区分的条目——(1)年度原始构造AssetGrowth（Table2, clear predictor）：样本1968-2003，t=7.64，与原文自身port sort的t=8.5高度吻合；(2)季度重构版AssetGrowth_q（Table4, Indirect Evidence/HXZ variant，即C&amp;Z在测试HXZ自创的季度化变量，而非Cooper-Gulen-Schill原始年度变量）：t=4.84。因此表面的HXZ-vs-C&amp;Z分歧，实际混合了断点/权重效应(年度对比下HXZ量级仅42%)与变量重构效应(年度vs季度)两个不同维度，值得在论文中分开讨论。</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Asset Growth and Stock Returns</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Cooper, Gulen and Schill (2008)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>AssetGrowth</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="17.2" customHeight="1">
-      <c r="A4" s="6" t="n">
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="34" customHeight="1" spans="1:5">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="51" customHeight="1" spans="1:5">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>需区分两个变量，现有note把二者混为一谈：(1) O-score(Dichev原始构造，真正的分歧案例)：HXZ在全部四种断点/权重组合下均不显著(NYSE-VW t=0.48, NYSE-EW t=0.04, All-VW t=1.82, All-EW t=0.40)，说明失败并非断点或权重选择所致；C&amp;Z的OScore为clear predictor,t=3.39(样本1981-1995)。可能原因是Dichev原文采用非对称的“最高10%-最低70%”分组，而HXZ改用标准对称十分位。(2) Z-score：C&amp;Z自身也将其归类为Not Predictor(t≈1.20-1.59)，与HXZ失败结论一致，并非分歧案例——建议本行聚焦O-score，或将两者拆成独立两行。</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Is the risk of bankruptcy a systematic risk </t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Dichev (1998)</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>ZScore/oscore</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="6" t="n">
+      <c r="B3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="34" customHeight="1" spans="1:5">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>都成功且量级也接近：HXZ的R66(前6个月收益排序、持有6个月)组合，NYSE-VW 0.82%/月,t=3.5(扩展样本1967-2016)；在原文对应的较短样本+All-EW下达到1.18%/月,t=4.22，与原文Jegadeesh-Titman(1993)自身报告的1.1%/月,t=3.61非常接近；HXZ原始(较短)样本NYSE-VW为1.06%/月,t=3.82。C&amp;Z采用与原文一致的单一排序(single sort)构造，而非Fama-French式2x3双重排序，且发现该动量组合与其他long-short组合的相关性上限约0.6(仅少数组合达到)，支持其作为独立因子的稳健性。断点、权重、排序方式在此因子上带来的分歧都很小。</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Returns to buying winners and selling losers- Implications for stock market efficiency</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Jegadeesh and Titman (1993, JF)</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>momentum</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="6" t="n">
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="17" customHeight="1" spans="1:5">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" ht="17.2" customHeight="1" spans="1:5">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>原文DNR(1998)本身并非标准VW/EW quantile long-short检验：换手率=3个月滚动平均成交量/流通股数(t-3至t-1月)，核心检验是个股层面月度Fama-MacBeth横截面回归(控制规模、B/M)，全文从未报告VW或EW组合收益；文中基于Amihud-Mendelson(1986)方法的beta分组仅用于估计beta，与换手率排序无关。样本为NYSE非金融股1962.7-1991.12，月频。HXZ将其重构为Tur1并做标准quantile long-short：NYSE-VW t=0.61(失败)，All-EW t=4.22(强，呈现典型microcap驱动模式)；C&amp;Z的ShareVol为clear predictor,t=3.87(样本1962-1991)，原文自身univariate回归t=8.9。由于原文根本不存在VW/EW组合排序这一维度，HXZ与C&amp;Z各自的quantile框架都是后续再造而非对原文的还原，这一点本身就是论文里值得强调的方法论发现。</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Liquidity and stock returns: An alternative test</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Datar, V. T., Naik, N. Y., and Radcliffe, R. (1998)</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>ShareVol</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="6" t="n">
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" ht="17" customHeight="1" spans="1:5">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>原文与C&amp;Z均采用双重排序(double sort)构造，区别于同表其他单一排序因子。HXZ的Sr变量(5年销售增长率排名)：NYSE-VW t=1.08(失败)，NYSE-EW t=3.52，All-EW t=3.65，呈现典型的microcap驱动模式(EW远强于VW，全市场断点强于NYSE断点)；C&amp;Z的MeanRankRevGrowth为clear predictor(双重排序)，t=3.94(样本1968-1990)，与原文自身双重排序t=4.5高度吻合。分歧主要来自断点(NYSE vs 全市场)与权重(VW vs EW)选择的叠加效应。</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Contrarian Investment, Extrapolation, and Risk</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Lakonishok, Josef, Andrei Shleifer, and Robert W. Vishny (1994)</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>MeanRankRevGrowth</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="n"/>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="n"/>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="n"/>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n"/>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-    </row>
-    <row r="12" ht="100" customHeight="1">
-      <c r="A12" s="6" t="n"/>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="n"/>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="n"/>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-    </row>
-    <row r="15" ht="17.2" customHeight="1">
-      <c r="A15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="E15" s="7" t="n"/>
-    </row>
-    <row r="16" ht="17.2" customHeight="1">
-      <c r="A16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
-      <c r="E16" s="7" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="n"/>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="n"/>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="n"/>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="n"/>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="n"/>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="n"/>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
+      <c r="B7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+    </row>
+    <row r="10" ht="100" customHeight="1" spans="1:5">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="7"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="7"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+    </row>
+    <row r="13" ht="17.2" customHeight="1" spans="1:5">
+      <c r="A13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="E13" s="6"/>
+    </row>
+    <row r="14" ht="17.2" customHeight="1" spans="1:5">
+      <c r="A14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="E14" s="6"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>